--- a/data/trans_orig/P24D-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P24D-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha intentado alguna vez dejar de fumar en 2007</t>
+          <t>Población según si ha intentado alguna vez dejar de fumar en 2007 (tasa de respuesta: 99,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>54397</t>
+          <t>53742</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>77502</t>
+          <t>78207</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25282</t>
+          <t>25478</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43816</t>
+          <t>44705</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>84262</t>
+          <t>85065</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>114524</t>
+          <t>115820</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>48,19%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72656</t>
+          <t>71951</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>95761</t>
+          <t>96416</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46371</t>
+          <t>45482</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64905</t>
+          <t>64709</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>125821</t>
+          <t>124525</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>156083</t>
+          <t>155280</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,61%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32588</t>
+          <t>33393</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56800</t>
+          <t>55758</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37926</t>
+          <t>37407</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60697</t>
+          <t>59850</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>76210</t>
+          <t>75840</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>109798</t>
+          <t>107921</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>40,41%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>78368</t>
+          <t>79410</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>102580</t>
+          <t>101775</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>71230</t>
+          <t>72077</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>94001</t>
+          <t>94520</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>157297</t>
+          <t>159174</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>190885</t>
+          <t>191255</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,61%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>67725</t>
+          <t>65735</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>98264</t>
+          <t>96373</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10238</t>
+          <t>9492</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22911</t>
+          <t>22678</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>82398</t>
+          <t>81780</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>114100</t>
+          <t>114795</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,51%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>155703</t>
+          <t>157594</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>186242</t>
+          <t>188232</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21195</t>
+          <t>21428</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33868</t>
+          <t>34614</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>183973</t>
+          <t>183278</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>215675</t>
+          <t>216293</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,56%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>152187</t>
+          <t>151116</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>195135</t>
+          <t>194442</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>72036</t>
+          <t>71767</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101670</t>
+          <t>100679</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>232470</t>
+          <t>228089</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>287227</t>
+          <t>283784</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,37%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>367598</t>
+          <t>368291</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>410546</t>
+          <t>411617</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>137883</t>
+          <t>138874</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>167517</t>
+          <t>167786</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>515059</t>
+          <t>518502</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>569816</t>
+          <t>574197</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>71,57%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38617</t>
+          <t>39579</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>63166</t>
+          <t>63842</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47474</t>
+          <t>46357</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>73890</t>
+          <t>73864</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>93268</t>
+          <t>93058</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>129217</t>
+          <t>130260</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,58%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>124458</t>
+          <t>123782</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>149007</t>
+          <t>148045</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>104568</t>
+          <t>104594</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>130984</t>
+          <t>132101</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>236865</t>
+          <t>235822</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>272814</t>
+          <t>273024</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,58%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>2414</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11211</t>
+          <t>11241</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42229</t>
+          <t>43003</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>65484</t>
+          <t>66310</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46972</t>
+          <t>46073</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>74281</t>
+          <t>74549</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>29,02%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>76494</t>
+          <t>76464</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>85775</t>
+          <t>85291</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>103687</t>
+          <t>102861</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>126942</t>
+          <t>126168</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>182595</t>
+          <t>182327</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>209904</t>
+          <t>210803</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>82,06%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>382408</t>
+          <t>382918</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>454732</t>
+          <t>456890</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>270244</t>
+          <t>270813</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>327726</t>
+          <t>324764</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>673058</t>
+          <t>675327</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>765056</t>
+          <t>765894</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,33%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>922624</t>
+          <t>920466</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>994948</t>
+          <t>994438</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>525675</t>
+          <t>528637</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>583157</t>
+          <t>582588</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1465701</t>
+          <t>1464863</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1557699</t>
+          <t>1555430</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>69,73%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha intentado alguna vez dejar de fumar en 2012</t>
+          <t>Población según si ha intentado alguna vez dejar de fumar en 2012 (tasa de respuesta: 99,63%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>70718</t>
+          <t>69684</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>96176</t>
+          <t>94025</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41486</t>
+          <t>42241</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62685</t>
+          <t>61592</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>118226</t>
+          <t>118950</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>150192</t>
+          <t>150396</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>60,84%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52130</t>
+          <t>54281</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77588</t>
+          <t>78622</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36194</t>
+          <t>37287</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57393</t>
+          <t>56638</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>96993</t>
+          <t>96789</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>128959</t>
+          <t>128235</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>51,88%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65834</t>
+          <t>67142</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92978</t>
+          <t>93136</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>63654</t>
+          <t>61700</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>87639</t>
+          <t>85898</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>138818</t>
+          <t>137457</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>172718</t>
+          <t>172618</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>62,94%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>57498</t>
+          <t>57340</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>84642</t>
+          <t>83334</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36149</t>
+          <t>37890</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>60134</t>
+          <t>62088</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>101546</t>
+          <t>101646</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>135446</t>
+          <t>136807</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,88%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>122102</t>
+          <t>124221</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>156858</t>
+          <t>158030</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29061</t>
+          <t>28934</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47923</t>
+          <t>46916</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>159104</t>
+          <t>157780</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>196474</t>
+          <t>197592</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>55,32%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>115081</t>
+          <t>113909</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>149837</t>
+          <t>147718</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37325</t>
+          <t>38332</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56187</t>
+          <t>56314</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>160713</t>
+          <t>159595</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>198083</t>
+          <t>199407</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>55,83%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>211679</t>
+          <t>209232</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>256799</t>
+          <t>257812</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>132611</t>
+          <t>133200</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>167374</t>
+          <t>169426</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>355815</t>
+          <t>355510</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>411624</t>
+          <t>413251</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,97%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>242592</t>
+          <t>241579</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>287712</t>
+          <t>290159</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>113330</t>
+          <t>111278</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>148093</t>
+          <t>147504</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>368470</t>
+          <t>366843</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>424279</t>
+          <t>424584</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>54,43%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>64176</t>
+          <t>64403</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>92450</t>
+          <t>91694</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>95933</t>
+          <t>96981</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>127999</t>
+          <t>128970</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>168148</t>
+          <t>166894</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>212123</t>
+          <t>210309</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>48,61%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>124770</t>
+          <t>125526</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>153044</t>
+          <t>152817</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>87447</t>
+          <t>86476</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>119513</t>
+          <t>118465</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>220542</t>
+          <t>222356</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>264517</t>
+          <t>265771</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>61,43%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6880</t>
+          <t>6884</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18479</t>
+          <t>19403</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54903</t>
+          <t>53913</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>81067</t>
+          <t>80344</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>65188</t>
+          <t>65828</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>94463</t>
+          <t>94492</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,67%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>44072</t>
+          <t>43148</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>55671</t>
+          <t>55667</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>83123</t>
+          <t>83846</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>109287</t>
+          <t>110277</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>132278</t>
+          <t>132249</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>161553</t>
+          <t>160913</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>70,97%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>585448</t>
+          <t>588633</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>663346</t>
+          <t>667283</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>467081</t>
+          <t>464976</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>530613</t>
+          <t>528909</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1070713</t>
+          <t>1077109</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1174922</t>
+          <t>1173542</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>50,62%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>686536</t>
+          <t>682599</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>764434</t>
+          <t>761249</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>437643</t>
+          <t>439347</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>501175</t>
+          <t>503280</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1143215</t>
+          <t>1144595</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1247424</t>
+          <t>1241028</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,54%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha intentado alguna vez dejar de fumar en 2016</t>
+          <t>Población según si ha intentado alguna vez dejar de fumar en 2016 (tasa de respuesta: 99,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49666</t>
+          <t>48762</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70254</t>
+          <t>70190</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>66,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27228</t>
+          <t>28440</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44056</t>
+          <t>43587</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>82440</t>
+          <t>81481</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>110831</t>
+          <t>109560</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>63,4%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36070</t>
+          <t>36134</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56658</t>
+          <t>57562</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22425</t>
+          <t>22894</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39253</t>
+          <t>38041</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>61974</t>
+          <t>63245</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>90365</t>
+          <t>91324</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,85%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42480</t>
+          <t>40622</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63740</t>
+          <t>62475</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32498</t>
+          <t>33250</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53652</t>
+          <t>52504</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>81424</t>
+          <t>78930</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>109400</t>
+          <t>108928</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,23%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40854</t>
+          <t>42119</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>62114</t>
+          <t>63972</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>46405</t>
+          <t>47553</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>67559</t>
+          <t>66807</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>95250</t>
+          <t>95722</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>123226</t>
+          <t>125720</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>61,43%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>84573</t>
+          <t>84709</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>114196</t>
+          <t>115284</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20143</t>
+          <t>20432</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34764</t>
+          <t>34759</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>110202</t>
+          <t>112441</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>143627</t>
+          <t>144387</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>53,63%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>102542</t>
+          <t>101454</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>132165</t>
+          <t>132029</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>60,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17739</t>
+          <t>17744</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32360</t>
+          <t>32071</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>125614</t>
+          <t>124854</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>159039</t>
+          <t>156800</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>58,24%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>163011</t>
+          <t>165599</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>205249</t>
+          <t>204980</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>127505</t>
+          <t>127901</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>162590</t>
+          <t>162632</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>303828</t>
+          <t>303695</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>357541</t>
+          <t>358637</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,07%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>224945</t>
+          <t>225214</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>267183</t>
+          <t>264595</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>153223</t>
+          <t>153181</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>188308</t>
+          <t>187912</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>388466</t>
+          <t>387370</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>442179</t>
+          <t>442312</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,29%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>72864</t>
+          <t>73798</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>104030</t>
+          <t>103449</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>81544</t>
+          <t>81776</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>110683</t>
+          <t>111270</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>163249</t>
+          <t>162839</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>204935</t>
+          <t>207007</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>45,36%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>137193</t>
+          <t>137774</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>168359</t>
+          <t>167425</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>104411</t>
+          <t>103824</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>133550</t>
+          <t>133318</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>251382</t>
+          <t>249310</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>293068</t>
+          <t>293478</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,31%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12630</t>
+          <t>12954</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28637</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49013</t>
+          <t>47349</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>74050</t>
+          <t>74570</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>66013</t>
+          <t>65043</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>98063</t>
+          <t>95770</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>39,25%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43318</t>
+          <t>44687</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>59325</t>
+          <t>59001</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>97980</t>
+          <t>97460</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>123017</t>
+          <t>124681</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>145922</t>
+          <t>148215</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>177972</t>
+          <t>178942</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>73,34%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>469450</t>
+          <t>469887</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>538698</t>
+          <t>538652</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>377594</t>
+          <t>379914</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>439527</t>
+          <t>442177</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>866329</t>
+          <t>864810</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>959633</t>
+          <t>956682</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>45,71%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>632328</t>
+          <t>632374</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>701576</t>
+          <t>701139</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>482452</t>
+          <t>479802</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>544385</t>
+          <t>542065</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1133372</t>
+          <t>1136323</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1226676</t>
+          <t>1228195</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,68%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha intentado alguna vez dejar de fumar en 2023</t>
+          <t>Población según si ha intentado alguna vez dejar de fumar en 2023 (tasa de respuesta: 99,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27964</t>
+          <t>28244</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46900</t>
+          <t>47042</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26047</t>
+          <t>26479</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39935</t>
+          <t>39861</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59515</t>
+          <t>59960</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>82223</t>
+          <t>82580</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>54,04%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37992</t>
+          <t>37850</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56928</t>
+          <t>56648</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27978</t>
+          <t>28052</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41866</t>
+          <t>41434</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>70582</t>
+          <t>70225</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>93290</t>
+          <t>92845</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>60,76%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25885</t>
+          <t>26187</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45928</t>
+          <t>45802</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27152</t>
+          <t>27533</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43147</t>
+          <t>43176</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>59252</t>
+          <t>59444</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84185</t>
+          <t>83936</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,66%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46789</t>
+          <t>46915</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>66832</t>
+          <t>66530</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40258</t>
+          <t>40229</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>56253</t>
+          <t>55872</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>91937</t>
+          <t>92186</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>116870</t>
+          <t>116678</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,25%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28865</t>
+          <t>29144</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52500</t>
+          <t>51720</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8177</t>
+          <t>7738</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16007</t>
+          <t>15754</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40967</t>
+          <t>39625</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64913</t>
+          <t>62700</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>43,08%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67561</t>
+          <t>68341</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>91196</t>
+          <t>90917</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9485</t>
+          <t>9738</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17315</t>
+          <t>17754</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>80640</t>
+          <t>82853</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>104586</t>
+          <t>105928</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>72,78%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>102119</t>
+          <t>105656</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>149045</t>
+          <t>150912</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>86263</t>
+          <t>85936</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>112433</t>
+          <t>111303</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>199930</t>
+          <t>200705</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>251125</t>
+          <t>247959</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>44,96%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>189433</t>
+          <t>187566</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>236359</t>
+          <t>232822</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>100641</t>
+          <t>101771</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>126811</t>
+          <t>127138</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>300427</t>
+          <t>303593</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>351622</t>
+          <t>350847</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,61%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33758</t>
+          <t>34790</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58982</t>
+          <t>59672</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>55730</t>
+          <t>54654</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77164</t>
+          <t>77203</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>96105</t>
+          <t>95057</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>128503</t>
+          <t>129096</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>41,25%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>96128</t>
+          <t>95438</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>121352</t>
+          <t>120320</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>80679</t>
+          <t>80640</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>102113</t>
+          <t>103189</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>184451</t>
+          <t>183858</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>216849</t>
+          <t>217897</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,63%</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9940</t>
+          <t>11805</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23976</t>
+          <t>24749</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41941</t>
+          <t>43513</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25377</t>
+          <t>25727</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>45683</t>
+          <t>46116</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>42,04%</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15024</t>
+          <t>13159</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42784</t>
+          <t>41212</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>60749</t>
+          <t>59976</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>64005</t>
+          <t>63572</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>84311</t>
+          <t>83961</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,55%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>255846</t>
+          <t>258159</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>317254</t>
+          <t>323453</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>256705</t>
+          <t>255736</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>299220</t>
+          <t>298698</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>528142</t>
+          <t>527091</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>606023</t>
+          <t>610469</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>42,14%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>498968</t>
+          <t>492769</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>560376</t>
+          <t>558063</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>333232</t>
+          <t>333754</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>375747</t>
+          <t>376716</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>842651</t>
+          <t>838205</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>920532</t>
+          <t>921583</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,62%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P24D-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P24D-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53742</t>
+          <t>53862</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>78207</t>
+          <t>77596</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25478</t>
+          <t>25358</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44705</t>
+          <t>43271</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>85065</t>
+          <t>84623</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>115820</t>
+          <t>115972</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,25%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71951</t>
+          <t>72562</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>96416</t>
+          <t>96296</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45482</t>
+          <t>46916</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64709</t>
+          <t>64829</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>124525</t>
+          <t>124373</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>155280</t>
+          <t>155722</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,79%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33393</t>
+          <t>31623</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55758</t>
+          <t>55409</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37407</t>
+          <t>36990</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>59850</t>
+          <t>58555</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>75840</t>
+          <t>75656</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>107921</t>
+          <t>107044</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,08%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>79410</t>
+          <t>79759</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>101775</t>
+          <t>103545</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>72077</t>
+          <t>73372</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>94520</t>
+          <t>94937</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>159174</t>
+          <t>160051</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>191255</t>
+          <t>191439</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>71,67%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65735</t>
+          <t>66875</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>96373</t>
+          <t>96982</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9492</t>
+          <t>9984</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22678</t>
+          <t>22028</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>81780</t>
+          <t>81298</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>114795</t>
+          <t>112893</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>37,87%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>157594</t>
+          <t>156985</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>188232</t>
+          <t>187092</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21428</t>
+          <t>22078</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34614</t>
+          <t>34122</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>183278</t>
+          <t>185180</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>216293</t>
+          <t>216775</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,73%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>151116</t>
+          <t>148253</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>194442</t>
+          <t>193492</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71767</t>
+          <t>72626</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>100679</t>
+          <t>101491</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>228089</t>
+          <t>232617</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>283784</t>
+          <t>284898</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,51%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>368291</t>
+          <t>369241</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>411617</t>
+          <t>414480</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>138874</t>
+          <t>138062</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>167786</t>
+          <t>166927</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>518502</t>
+          <t>517388</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>574197</t>
+          <t>569669</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,01%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39579</t>
+          <t>38892</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>63842</t>
+          <t>62797</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>46357</t>
+          <t>46987</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>73864</t>
+          <t>73004</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>93058</t>
+          <t>91841</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>130260</t>
+          <t>128708</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,16%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>123782</t>
+          <t>124827</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>148045</t>
+          <t>148732</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>104594</t>
+          <t>105454</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>132101</t>
+          <t>131471</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>235822</t>
+          <t>237374</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>273024</t>
+          <t>274241</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,91%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2414</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11241</t>
+          <t>11523</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43003</t>
+          <t>42440</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>66310</t>
+          <t>66897</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46073</t>
+          <t>47519</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>74549</t>
+          <t>73569</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,64%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>76464</t>
+          <t>76182</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>85291</t>
+          <t>85686</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>102861</t>
+          <t>102274</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>126168</t>
+          <t>126731</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>182327</t>
+          <t>183307</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>210803</t>
+          <t>209357</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>81,5%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>382918</t>
+          <t>386262</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>456890</t>
+          <t>455803</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>270813</t>
+          <t>268655</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>324764</t>
+          <t>325686</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>675327</t>
+          <t>673341</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>765894</t>
+          <t>763968</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,25%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>920466</t>
+          <t>921553</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>994438</t>
+          <t>991094</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>528637</t>
+          <t>527715</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>582588</t>
+          <t>584746</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1464863</t>
+          <t>1466789</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1555430</t>
+          <t>1557416</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>69,82%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>69684</t>
+          <t>68595</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>94025</t>
+          <t>94268</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42241</t>
+          <t>42082</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61592</t>
+          <t>62283</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>118950</t>
+          <t>118841</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>150396</t>
+          <t>150720</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>60,97%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54281</t>
+          <t>54038</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>78622</t>
+          <t>79711</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37287</t>
+          <t>36596</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56638</t>
+          <t>56797</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>96789</t>
+          <t>96465</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>128235</t>
+          <t>128344</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>51,92%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67142</t>
+          <t>65814</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>93136</t>
+          <t>93281</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61700</t>
+          <t>63108</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>85898</t>
+          <t>87142</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>137457</t>
+          <t>137344</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>172618</t>
+          <t>173688</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>63,33%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>57340</t>
+          <t>57195</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>83334</t>
+          <t>84662</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>37890</t>
+          <t>36646</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>62088</t>
+          <t>60680</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>101646</t>
+          <t>100576</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>136807</t>
+          <t>136920</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>49,92%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>124221</t>
+          <t>122640</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>158030</t>
+          <t>156383</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28934</t>
+          <t>28507</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46916</t>
+          <t>47186</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>55,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>157780</t>
+          <t>156605</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>197592</t>
+          <t>196696</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>55,07%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>113909</t>
+          <t>115556</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>147718</t>
+          <t>149299</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38332</t>
+          <t>38062</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56314</t>
+          <t>56741</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>159595</t>
+          <t>160491</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>199407</t>
+          <t>200582</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>56,16%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>209232</t>
+          <t>209382</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>257812</t>
+          <t>255684</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>133200</t>
+          <t>132270</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>169426</t>
+          <t>168045</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>355510</t>
+          <t>356915</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>413251</t>
+          <t>413175</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>52,96%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>241579</t>
+          <t>243707</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>290159</t>
+          <t>290009</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>111278</t>
+          <t>112659</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>147504</t>
+          <t>148434</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>366843</t>
+          <t>366919</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>424584</t>
+          <t>423179</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,25%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>64403</t>
+          <t>64115</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>91694</t>
+          <t>91805</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>96981</t>
+          <t>96738</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>128970</t>
+          <t>127815</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>166894</t>
+          <t>168318</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>210309</t>
+          <t>211258</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>48,83%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>125526</t>
+          <t>125415</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>152817</t>
+          <t>153105</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>86476</t>
+          <t>87631</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>118465</t>
+          <t>118708</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>222356</t>
+          <t>221407</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>265771</t>
+          <t>264347</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,1%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6884</t>
+          <t>7668</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19403</t>
+          <t>19860</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>53913</t>
+          <t>55063</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>80344</t>
+          <t>79938</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>65828</t>
+          <t>66014</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>94492</t>
+          <t>94005</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,46%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43148</t>
+          <t>42691</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>55667</t>
+          <t>54883</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>83846</t>
+          <t>84252</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>110277</t>
+          <t>109127</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>132249</t>
+          <t>132736</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>160913</t>
+          <t>160727</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>70,89%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>588633</t>
+          <t>587898</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>667283</t>
+          <t>670505</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>464976</t>
+          <t>461093</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>528909</t>
+          <t>527618</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1077109</t>
+          <t>1071267</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1173542</t>
+          <t>1173467</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>682599</t>
+          <t>679377</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>761249</t>
+          <t>761984</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>439347</t>
+          <t>440638</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>503280</t>
+          <t>507163</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1144595</t>
+          <t>1144670</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1241028</t>
+          <t>1246870</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,79%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48762</t>
+          <t>49260</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70190</t>
+          <t>71270</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28440</t>
+          <t>28004</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43587</t>
+          <t>44416</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>81481</t>
+          <t>81147</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>109560</t>
+          <t>108001</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>62,5%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36134</t>
+          <t>35054</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57562</t>
+          <t>57064</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22894</t>
+          <t>22065</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38041</t>
+          <t>38477</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>63245</t>
+          <t>64804</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>91324</t>
+          <t>91658</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>53,04%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40622</t>
+          <t>40747</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62475</t>
+          <t>62439</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33250</t>
+          <t>33000</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52504</t>
+          <t>52684</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>78930</t>
+          <t>79950</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>108928</t>
+          <t>108924</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>53,22%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42119</t>
+          <t>42155</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>63972</t>
+          <t>63847</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>47553</t>
+          <t>47373</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>66807</t>
+          <t>67057</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>95722</t>
+          <t>95726</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>125720</t>
+          <t>124700</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>60,93%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>84709</t>
+          <t>84110</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>115284</t>
+          <t>114422</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20432</t>
+          <t>20104</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34759</t>
+          <t>34190</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>112441</t>
+          <t>109294</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>144387</t>
+          <t>144674</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,73%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>101454</t>
+          <t>102316</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>132029</t>
+          <t>132628</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17744</t>
+          <t>18313</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32071</t>
+          <t>32399</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>124854</t>
+          <t>124567</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>156800</t>
+          <t>159947</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>59,41%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>165599</t>
+          <t>163328</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>204980</t>
+          <t>205250</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>127901</t>
+          <t>127539</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>162632</t>
+          <t>163934</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>303695</t>
+          <t>303743</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>358637</t>
+          <t>360830</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,37%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>225214</t>
+          <t>224944</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>264595</t>
+          <t>266866</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>153181</t>
+          <t>151879</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>187912</t>
+          <t>188274</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>387370</t>
+          <t>385177</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>442312</t>
+          <t>442264</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>59,28%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>73798</t>
+          <t>73710</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>103449</t>
+          <t>103288</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>81776</t>
+          <t>82181</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>111270</t>
+          <t>111316</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>162839</t>
+          <t>163847</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>207007</t>
+          <t>204607</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>44,84%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>137774</t>
+          <t>137935</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>167425</t>
+          <t>167513</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>103824</t>
+          <t>103778</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>133318</t>
+          <t>132913</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>249310</t>
+          <t>251710</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>293478</t>
+          <t>292470</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>64,09%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12954</t>
+          <t>13044</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>28103</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47349</t>
+          <t>48246</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>74570</t>
+          <t>75511</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>65043</t>
+          <t>64988</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>95770</t>
+          <t>95501</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,14%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>44687</t>
+          <t>43852</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>59001</t>
+          <t>58911</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>97460</t>
+          <t>96519</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>124681</t>
+          <t>123784</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>148215</t>
+          <t>148484</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>178942</t>
+          <t>178997</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,75%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,36%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>469887</t>
+          <t>469630</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>538652</t>
+          <t>537788</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,82 +8076,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>45,92%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>409409</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>381797</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>441009</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>44,41%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>41,41%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>47,83%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>864</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>913481</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>869421</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>962778</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>43,64%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>41,54%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>46,0%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>395</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>409409</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>379914</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>442177</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>41,21%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>47,96%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>864</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>913481</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>864810</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>956682</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>43,64%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>41,32%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>45,71%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>632374</t>
+          <t>633238</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>701139</t>
+          <t>701396</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,82 +8189,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>54,08%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>59,9%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>498</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>512570</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>480970</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>540182</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>55,59%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>52,17%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>58,59%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1119</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>1179524</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>1130227</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>1223584</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>56,36%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>54,0%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>59,87%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>498</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>512570</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>479802</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>542065</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>55,59%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>52,04%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>58,79%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1119</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1179524</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1136323</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1228195</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>56,36%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>54,29%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>58,46%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>37389</t>
+          <t>43740</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28244</t>
+          <t>33367</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47042</t>
+          <t>53908</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>33350</t>
+          <t>34715</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26479</t>
+          <t>27981</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39861</t>
+          <t>41433</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>70739</t>
+          <t>78454</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59960</t>
+          <t>66353</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>82580</t>
+          <t>90749</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>54,63%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>47503</t>
+          <t>50541</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37850</t>
+          <t>40373</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56648</t>
+          <t>60914</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>34563</t>
+          <t>37128</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28052</t>
+          <t>30410</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41434</t>
+          <t>43862</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>82066</t>
+          <t>87670</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>70225</t>
+          <t>75375</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>92845</t>
+          <t>99771</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>60,06%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>84892</t>
+          <t>94281</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>84892</t>
+          <t>94281</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>84892</t>
+          <t>94281</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>67913</t>
+          <t>71843</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>67913</t>
+          <t>71843</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>67913</t>
+          <t>71843</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>152805</t>
+          <t>166124</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>152805</t>
+          <t>166124</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>152805</t>
+          <t>166124</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35817</t>
+          <t>37324</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26187</t>
+          <t>28465</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45802</t>
+          <t>49288</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35507</t>
+          <t>39889</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27533</t>
+          <t>31646</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43176</t>
+          <t>48383</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>71324</t>
+          <t>77213</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>59444</t>
+          <t>64801</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83936</t>
+          <t>91920</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>49,07%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>56900</t>
+          <t>57476</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46915</t>
+          <t>45512</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>66530</t>
+          <t>66335</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>47898</t>
+          <t>52620</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40229</t>
+          <t>44126</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>55872</t>
+          <t>60863</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>104798</t>
+          <t>110096</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>92186</t>
+          <t>95389</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>116678</t>
+          <t>122508</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>65,4%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>92717</t>
+          <t>94800</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>92717</t>
+          <t>94800</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>92717</t>
+          <t>94800</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>83405</t>
+          <t>92509</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>83405</t>
+          <t>92509</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>83405</t>
+          <t>92509</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>176122</t>
+          <t>187309</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>176122</t>
+          <t>187309</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>176122</t>
+          <t>187309</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>39833</t>
+          <t>42756</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29144</t>
+          <t>32125</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51720</t>
+          <t>55996</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11918</t>
+          <t>12547</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7738</t>
+          <t>8571</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15754</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>51751</t>
+          <t>55303</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39625</t>
+          <t>43398</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62700</t>
+          <t>68822</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>44,42%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>80228</t>
+          <t>84858</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>68341</t>
+          <t>71618</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>90917</t>
+          <t>95489</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13574</t>
+          <t>14787</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9738</t>
+          <t>10453</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17754</t>
+          <t>18763</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>93802</t>
+          <t>99645</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>82853</t>
+          <t>86126</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>105928</t>
+          <t>111550</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>71,99%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>120061</t>
+          <t>127614</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>120061</t>
+          <t>127614</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>120061</t>
+          <t>127614</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>25492</t>
+          <t>27334</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25492</t>
+          <t>27334</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25492</t>
+          <t>27334</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>145553</t>
+          <t>154948</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>145553</t>
+          <t>154948</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>145553</t>
+          <t>154948</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>126232</t>
+          <t>132545</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>105656</t>
+          <t>111656</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>150912</t>
+          <t>153797</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>99203</t>
+          <t>108747</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>85936</t>
+          <t>94643</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>111303</t>
+          <t>122931</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>225435</t>
+          <t>241292</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>200705</t>
+          <t>217535</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>247959</t>
+          <t>267858</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>45,1%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>212246</t>
+          <t>230746</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>187566</t>
+          <t>209494</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>232822</t>
+          <t>251635</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>113871</t>
+          <t>121826</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>101771</t>
+          <t>107642</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>127138</t>
+          <t>135930</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>326117</t>
+          <t>352572</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>303593</t>
+          <t>326006</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>350847</t>
+          <t>376329</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>63,37%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>338478</t>
+          <t>363291</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>338478</t>
+          <t>363291</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>338478</t>
+          <t>363291</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>213074</t>
+          <t>230573</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>213074</t>
+          <t>230573</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>213074</t>
+          <t>230573</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>551552</t>
+          <t>593864</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>551552</t>
+          <t>593864</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>551552</t>
+          <t>593864</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>46072</t>
+          <t>57735</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34790</t>
+          <t>43495</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59672</t>
+          <t>71909</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>65942</t>
+          <t>72374</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>54654</t>
+          <t>61320</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77203</t>
+          <t>84530</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>112015</t>
+          <t>130109</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>95057</t>
+          <t>113873</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>129096</t>
+          <t>149753</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>42,49%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>109038</t>
+          <t>121998</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>95438</t>
+          <t>107824</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>120320</t>
+          <t>136238</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>91901</t>
+          <t>100323</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>80640</t>
+          <t>88167</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>103189</t>
+          <t>111377</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>200939</t>
+          <t>222320</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>183858</t>
+          <t>202676</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>217897</t>
+          <t>238556</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>67,69%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>155110</t>
+          <t>179733</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>155110</t>
+          <t>179733</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>155110</t>
+          <t>179733</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>157843</t>
+          <t>172697</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>157843</t>
+          <t>172697</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>157843</t>
+          <t>172697</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>312954</t>
+          <t>352429</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>312954</t>
+          <t>352429</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>312954</t>
+          <t>352429</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,7 +10348,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1753</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11805</t>
+          <t>8710</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>32920</t>
+          <t>34745</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24749</t>
+          <t>26553</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43513</t>
+          <t>44989</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>34910</t>
+          <t>36499</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25727</t>
+          <t>27128</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46116</t>
+          <t>48026</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>42,27%</t>
         </is>
       </c>
     </row>
@@ -10461,27 +10461,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>22974</t>
+          <t>21686</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13159</t>
+          <t>14729</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24964</t>
+          <t>23439</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>51805</t>
+          <t>55422</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>41212</t>
+          <t>45178</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>59976</t>
+          <t>63614</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>74778</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>63572</t>
+          <t>65581</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>83961</t>
+          <t>86479</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,12%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>24964</t>
+          <t>23439</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>24964</t>
+          <t>23439</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>24964</t>
+          <t>23439</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>84725</t>
+          <t>90167</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>84725</t>
+          <t>90167</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>84725</t>
+          <t>90167</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>109688</t>
+          <t>113607</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>109688</t>
+          <t>113607</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>109688</t>
+          <t>113607</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>287333</t>
+          <t>315851</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>258159</t>
+          <t>284750</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>323453</t>
+          <t>350504</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>278840</t>
+          <t>303017</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>255736</t>
+          <t>279424</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>298698</t>
+          <t>328341</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>566174</t>
+          <t>618868</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>527091</t>
+          <t>579362</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>610469</t>
+          <t>658822</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,01%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>528889</t>
+          <t>567306</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>492769</t>
+          <t>532653</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>558063</t>
+          <t>598407</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>353612</t>
+          <t>382106</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>333754</t>
+          <t>356782</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>376716</t>
+          <t>405699</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>882500</t>
+          <t>949412</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>838205</t>
+          <t>909458</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>921583</t>
+          <t>988918</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,06%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>816222</t>
+          <t>883157</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>816222</t>
+          <t>883157</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>816222</t>
+          <t>883157</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>632452</t>
+          <t>685123</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>632452</t>
+          <t>685123</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>632452</t>
+          <t>685123</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1448674</t>
+          <t>1568280</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1448674</t>
+          <t>1568280</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1448674</t>
+          <t>1568280</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
